--- a/excel/FINANCE_CONTROL_PRO.xlsx
+++ b/excel/FINANCE_CONTROL_PRO.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,23 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +56,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,24 +426,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>FINANCE CONTROL PRO</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="2" ht="30" customHeight="1"/>
+    <row r="3" ht="15" customHeight="1"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Sistema inicial criado com sucesso</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>